--- a/results/monthly_investor_report_2026-10-01.xlsx
+++ b/results/monthly_investor_report_2026-10-01.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-03 07:11</t>
+          <t>Son Güncelleme: 2026-10-04 07:30</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -952,25 +952,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2569227197998707</v>
+        <v>0.2569227197998708</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>25692.27197998708</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0438354098267489</v>
+        <v>0.043835409826749</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1126.231271623031</v>
+        <v>1126.231271623034</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>425.8848472093135</v>
+        <v>425.8848472093136</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>387.6</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.8767081965349757</v>
+        <v>0.8767081965349784</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
@@ -995,16 +995,16 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1847809963640967</v>
+        <v>0.1847809963640966</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>18478.09963640967</v>
+        <v>18478.09963640966</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>0.0285714285714284</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>527.945703897416</v>
+        <v>527.9457038974157</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>398.0571428571428</v>
@@ -1013,7 +1013,7 @@
         <v>365.767852694762</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.5207736503606034</v>
+        <v>0.5207736503606021</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>0.0265059178623019</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>419.5788297265506</v>
+        <v>419.5788297265505</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>129.5450437015751</v>
@@ -1054,7 +1054,7 @@
         <v>116.8727931447235</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.3586333936512622</v>
+        <v>0.3586333936512606</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>40000</v>
+        <v>40000.00000000001</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-03 07:11</t>
+          <t>Son Güncelleme: 2026-10-04 07:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1353,19 +1353,19 @@
         <v>-0.02667302642785</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.0438354098267489</v>
+        <v>0.043835409826749</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.0795481196044297</v>
+        <v>0.0795481196044298</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>397.1174052174372</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>425.8848472093135</v>
+        <v>425.8848472093136</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>440.4556327986073</v>
+        <v>440.4556327986074</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>387.6</v>
@@ -1410,22 +1410,22 @@
         <v>-0.0166358032889645</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.0869050204659417</v>
+        <v>0.08690502046594149</v>
       </c>
       <c r="H9" s="18" t="n">
         <v>206.4081388876676</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>214.7839635538469</v>
+        <v>214.783963553847</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>228.1413571618594</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>199.4049942016601</v>
+        <v>199.4049942016602</v>
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-03 07:11</t>
+          <t>Son Güncelleme: 2026-10-04 07:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1776,7 +1776,7 @@
         <v>0.0194135163494683</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.0438354098267489</v>
+        <v>0.043835409826749</v>
       </c>
     </row>
     <row r="5">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>-0.0145540192653316</v>
+        <v>-0.0145540192653313</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.1070674427187814</v>
+        <v>0.1070674427187816</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>0.0870014876331113</v>
+        <v>0.0870014876331117</v>
       </c>
       <c r="H5" s="19" t="n">
         <v>0.0617187790758331</v>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="J5" s="19" t="n">
-        <v>0.0209011161906187</v>
+        <v>0.0209011161906186</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
     </row>
     <row r="6">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="J6" s="16" t="n">
-        <v>0.0274317148646485</v>
+        <v>0.0274317148646486</v>
       </c>
       <c r="K6" s="16" t="n">
         <v>0.0285714285714284</v>
@@ -1891,7 +1891,7 @@
         <v>-0.0991045140508395</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>-0.2507447940934695</v>
+        <v>-0.2507447940934696</v>
       </c>
       <c r="H7" s="19" t="n">
         <v>0.0145514515489975</v>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0439394170587713</v>
+        <v>-0.0439394170587712</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>-0.054681670799684</v>
+        <v>-0.0546816707996838</v>
       </c>
       <c r="G8" s="16" t="n">
         <v>-1.088185066944192e-06</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="E9" s="21" t="n">
-        <v>-0.0260638186703872</v>
+        <v>-0.0260638186703869</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>-0.0867830342807164</v>
+        <v>-0.08678303428071631</v>
       </c>
       <c r="G9" s="21" t="n">
         <v>0.3162383142651317</v>
@@ -2017,7 +2017,7 @@
         <v>-0.1024930747922437</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>-0.1916167418464079</v>
+        <v>-0.1916167418464081</v>
       </c>
       <c r="G10" s="21" t="n">
         <v>-0.2689530887272393</v>
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="J10" s="21" t="n">
-        <v>0.0155420014820778</v>
+        <v>0.0155420014820779</v>
       </c>
       <c r="K10" s="21" t="n">
         <v>0.0007363095911598</v>
@@ -2060,10 +2060,10 @@
         <v>0.0051440330833163</v>
       </c>
       <c r="F11" s="21" t="n">
-        <v>-0.0886194055078821</v>
+        <v>-0.088619405507882</v>
       </c>
       <c r="G11" s="21" t="n">
-        <v>-0.0860617815371082</v>
+        <v>-0.0860617815371079</v>
       </c>
       <c r="H11" s="21" t="n">
         <v>-0.1002489595618008</v>
@@ -2120,7 +2120,7 @@
         <v>0.0202251259166578</v>
       </c>
       <c r="K12" s="21" t="n">
-        <v>0.0394096913634611</v>
+        <v>0.0394096913634612</v>
       </c>
     </row>
     <row r="13">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="J14" s="23" t="n">
-        <v>0.0242756658707128</v>
+        <v>0.0242756658707127</v>
       </c>
       <c r="K14" s="23" t="n">
         <v>0.0096600462209198</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="J17" s="23" t="n">
-        <v>0.031484362145451</v>
+        <v>0.0314843621454511</v>
       </c>
       <c r="K17" s="23" t="n">
         <v>0.0414962223049317</v>
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="J18" s="23" t="n">
-        <v>0.0264489111327368</v>
+        <v>0.0264489111327367</v>
       </c>
       <c r="K18" s="23" t="n">
         <v>0.0523180466794031</v>
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="E20" s="23" t="n">
-        <v>-0.0450127465528696</v>
+        <v>-0.0450127465528694</v>
       </c>
       <c r="F20" s="23" t="n">
         <v>-0.1578709962992962</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="J20" s="23" t="n">
-        <v>0.0274993725325908</v>
+        <v>0.0274993725325907</v>
       </c>
       <c r="K20" s="23" t="n">
         <v>0.0328525399081489</v>
@@ -2497,7 +2497,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-03 07:11</t>
+          <t>Son Güncelleme: 2026-10-04 07:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2616,7 +2616,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-03 07:11</t>
+          <t>Son Güncelleme: 2026-10-04 07:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2867,7 +2867,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-03 07:11</t>
+          <t>Son Güncelleme: 2026-10-04 07:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2992,7 +2992,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-03 07:11</t>
+          <t>Son Güncelleme: 2026-10-04 07:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3069,7 +3069,7 @@
         <v>-52020.4065174628</v>
       </c>
       <c r="G4" s="24" t="n">
-        <v>19944351.64517885</v>
+        <v>19944351.64517886</v>
       </c>
       <c r="H4" s="25" t="n">
         <v>-0.1061733800350263</v>
@@ -3096,10 +3096,10 @@
         <v>0.0654822025202253</v>
       </c>
       <c r="F5" s="24" t="n">
-        <v>190313.8548415657</v>
+        <v>190313.8548415662</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>19944351.64517885</v>
+        <v>19944351.64517886</v>
       </c>
       <c r="H5" s="25" t="n">
         <v>-0.1061733800350263</v>
@@ -3129,7 +3129,7 @@
         <v>-9463.945294567529</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>19944351.64517885</v>
+        <v>19944351.64517886</v>
       </c>
       <c r="H6" s="25" t="n">
         <v>-0.1061733800350263</v>
@@ -3153,13 +3153,13 @@
         <v>126.1999969482422</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>-0.05397299308596093</v>
+        <v>-0.05397299308596082</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>-261375.0935518565</v>
+        <v>-261375.0935518555</v>
       </c>
       <c r="G7" s="24" t="n">
-        <v>19944351.64517885</v>
+        <v>19944351.64517886</v>
       </c>
       <c r="H7" s="25" t="n">
         <v>-0.1061733800350263</v>
@@ -3189,7 +3189,7 @@
         <v>17482.85022870218</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>19944351.64517885</v>
+        <v>19944351.64517886</v>
       </c>
       <c r="H8" s="25" t="n">
         <v>-0.1061733800350263</v>
@@ -3219,7 +3219,7 @@
         <v>-112795.0403937409</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>19944351.64517885</v>
+        <v>19944351.64517886</v>
       </c>
       <c r="H9" s="25" t="n">
         <v>-0.1061733800350263</v>
@@ -3249,7 +3249,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>19944351.64517885</v>
+        <v>19944351.64517886</v>
       </c>
       <c r="H10" s="25" t="n">
         <v>-0.1061733800350263</v>

--- a/results/monthly_investor_report_2026-10-01.xlsx
+++ b/results/monthly_investor_report_2026-10-01.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-04 07:30</t>
+          <t>Son Güncelleme: 2026-10-05 07:47</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1153,7 +1153,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-04 07:30</t>
+          <t>Son Güncelleme: 2026-10-05 07:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1665,7 +1665,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-04 07:30</t>
+          <t>Son Güncelleme: 2026-10-05 07:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2497,7 +2497,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-04 07:30</t>
+          <t>Son Güncelleme: 2026-10-05 07:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2616,7 +2616,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-04 07:30</t>
+          <t>Son Güncelleme: 2026-10-05 07:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2867,7 +2867,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-04 07:30</t>
+          <t>Son Güncelleme: 2026-10-05 07:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2992,7 +2992,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-04 07:30</t>
+          <t>Son Güncelleme: 2026-10-05 07:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
